--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_26.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_26.xlsx
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Smoker?</t>
+          <t>RiskTaking</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>Happiness</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-1.238654052345423</v>
+        <v>-1.652860950208004</v>
       </c>
       <c r="C2">
-        <v>0.0435015060008769</v>
+        <v>0.5491505649837364</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.1392496844998598</v>
+        <v>0.3197649321756758</v>
       </c>
       <c r="C3">
-        <v>0.8290578185183098</v>
+        <v>0.7590131030767842</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.2507303255299648</v>
+        <v>-0.1595974669451459</v>
       </c>
       <c r="C4">
-        <v>-0.07226061876191424</v>
+        <v>-0.6643639174901679</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.107547339808801</v>
+        <v>-1.561365194362166</v>
       </c>
       <c r="C5">
-        <v>0.575893465755651</v>
+        <v>0.07604750941305194</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.9283524965491985</v>
+        <v>-2.37308616880881</v>
       </c>
       <c r="C6">
-        <v>-0.5155522148255182</v>
+        <v>0.5722066023488153</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>1.179654635669571</v>
+        <v>2.14499672623334</v>
       </c>
       <c r="C7">
-        <v>-0.81884973372915</v>
+        <v>0.07103687444350293</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.6682524134378184</v>
+        <v>0.1965540757734972</v>
       </c>
       <c r="C8">
-        <v>1.016688543540887</v>
+        <v>2.181168111901861</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>1.629552105050554</v>
+        <v>-0.313499921438377</v>
       </c>
       <c r="C9">
-        <v>-0.6968350914084278</v>
+        <v>0.7449258022197969</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.6509717343495973</v>
+        <v>1.720455211441659</v>
       </c>
       <c r="C10">
-        <v>-0.08142919786356231</v>
+        <v>-1.405230542849895</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>1.21693014721964</v>
+        <v>1.204290565971801</v>
       </c>
       <c r="C11">
-        <v>0.6701031453455464</v>
+        <v>-0.8935488074987846</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>1.644677509816695</v>
+        <v>-1.143790392143049</v>
       </c>
       <c r="C12">
-        <v>1.247739436622743</v>
+        <v>0.3427100728521343</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-2.786662945264974</v>
+        <v>0.1202201359051362</v>
       </c>
       <c r="C13">
-        <v>1.13564293581491</v>
+        <v>0.1476305501314457</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.4817962383178986</v>
+        <v>0.6950823875489623</v>
       </c>
       <c r="C14">
-        <v>2.714992454006866</v>
+        <v>-1.025423668658525</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>1.329036326179303</v>
+        <v>-0.4490760485682291</v>
       </c>
       <c r="C15">
-        <v>-1.626505768122654</v>
+        <v>2.231499422983138</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.3559399540418743</v>
+        <v>-0.4088132612170578</v>
       </c>
       <c r="C16">
-        <v>0.2367672340927945</v>
+        <v>-0.6395814022334775</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>1.374160721602456</v>
+        <v>0.8493709887519948</v>
       </c>
       <c r="C17">
-        <v>-0.6857950187145871</v>
+        <v>-0.6130101050915322</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.4378216885210813</v>
+        <v>0.6456772864981526</v>
       </c>
       <c r="C18">
-        <v>0.9283954971674392</v>
+        <v>0.8164161748068022</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.8965159159496587</v>
+        <v>-1.205336956460445</v>
       </c>
       <c r="C19">
-        <v>0.2687601330789002</v>
+        <v>1.351071966113224</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.7226785264239418</v>
+        <v>-0.2330633014902488</v>
       </c>
       <c r="C20">
-        <v>-0.5142518502681016</v>
+        <v>-1.537331500962856</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>3.15611252342531</v>
+        <v>-0.0620026202084399</v>
       </c>
       <c r="C21">
-        <v>-0.8268368314598058</v>
+        <v>-0.7339640348024101</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>1.881242976009617</v>
+        <v>-0.3090340464499295</v>
       </c>
       <c r="C22">
-        <v>-1.247520848108191</v>
+        <v>-1.327358289587315</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>2.494940914387217</v>
+        <v>0.407634101621405</v>
       </c>
       <c r="C23">
-        <v>-0.08554222492083678</v>
+        <v>0.8032493869234525</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-1.791458668206088</v>
+        <v>0.3677906398189634</v>
       </c>
       <c r="C24">
-        <v>-0.9690078766818169</v>
+        <v>1.496771869001102</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.8730407384272317</v>
+        <v>-0.1929956706228485</v>
       </c>
       <c r="C25">
-        <v>1.5185966297787</v>
+        <v>-0.86675505372785</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-0.1830114324463282</v>
+        <v>0.5451707335412806</v>
       </c>
       <c r="C26">
-        <v>-2.152537406904976</v>
+        <v>-1.089795885218027</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-1.624715386832276</v>
+        <v>-2.587125975386657</v>
       </c>
       <c r="C27">
-        <v>1.509610706351327</v>
+        <v>1.219524561784044</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.4463014688561248</v>
+        <v>0.7735848743267405</v>
       </c>
       <c r="C28">
-        <v>-1.820198756308433</v>
+        <v>0.5030371228609207</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>2.220780818461801</v>
+        <v>-0.6545265370748006</v>
       </c>
       <c r="C29">
-        <v>-0.8321689315337939</v>
+        <v>-1.323055201080662</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.6655989853840558</v>
+        <v>-0.5546412440876521</v>
       </c>
       <c r="C30">
-        <v>-0.2483006921960423</v>
+        <v>0.9489800069990931</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.9066406071154609</v>
+        <v>-1.33102356849393</v>
       </c>
       <c r="C31">
-        <v>-1.848371395631045</v>
+        <v>-1.917904383284565</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-1.500105693828782</v>
+        <v>0.06118247666350653</v>
       </c>
       <c r="C32">
-        <v>-0.7001643478042211</v>
+        <v>0.2490656235531476</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.81248317803882</v>
+        <v>0.2137711358002719</v>
       </c>
       <c r="C33">
-        <v>1.659408365232496</v>
+        <v>0.7582928123013951</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>-0.8803895720533855</v>
+        <v>1.163224429517935</v>
       </c>
       <c r="C34">
-        <v>-0.5549905610975709</v>
+        <v>0.09190723069916384</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.9639123035907384</v>
+        <v>-0.398164076542673</v>
       </c>
       <c r="C35">
-        <v>0.6123230231629205</v>
+        <v>0.6240923868420325</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-1.098569510895834</v>
+        <v>0.1283250580472943</v>
       </c>
       <c r="C36">
-        <v>-0.9813177895358314</v>
+        <v>-0.6674556890979126</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.6812066584589499</v>
+        <v>-0.4216464159097097</v>
       </c>
       <c r="C37">
-        <v>1.627460867831592</v>
+        <v>-0.9306292383288474</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>0.06677273120450167</v>
+        <v>-0.590435463627154</v>
       </c>
       <c r="C38">
-        <v>0.8585192912729839</v>
+        <v>1.156525302702981</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.03058462850534547</v>
+        <v>1.566745300597648</v>
       </c>
       <c r="C39">
-        <v>1.227274535163777</v>
+        <v>-1.786216070637682</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.7390396068797677</v>
+        <v>-1.465440060701694</v>
       </c>
       <c r="C40">
-        <v>1.170751028222224</v>
+        <v>0.8807008385108948</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-1.565153251673133</v>
+        <v>-0.6132926127598136</v>
       </c>
       <c r="C41">
-        <v>-0.1310575183054763</v>
+        <v>-1.160786900447721</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.6027157057002041</v>
+        <v>2.08788675457296</v>
       </c>
       <c r="C42">
-        <v>-0.03230225500763858</v>
+        <v>-1.949594173373626</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-1.488658707814744</v>
+        <v>0.3349500584834669</v>
       </c>
       <c r="C43">
-        <v>0.9600673334737184</v>
+        <v>-1.667703581791811</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-0.08633433753347575</v>
+        <v>-0.5207631378856338</v>
       </c>
       <c r="C44">
-        <v>-0.3462038891482715</v>
+        <v>0.4854116635642609</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.08182589723100721</v>
+        <v>-2.005768541872917</v>
       </c>
       <c r="C45">
-        <v>0.354812635555986</v>
+        <v>-0.6866127444965808</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.3152236828831282</v>
+        <v>0.8008551776372812</v>
       </c>
       <c r="C46">
-        <v>0.5010609876238955</v>
+        <v>0.09273070270211142</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.3167843610639454</v>
+        <v>1.305051747834385</v>
       </c>
       <c r="C47">
-        <v>-0.06871073447619154</v>
+        <v>0.618264810736903</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.1919256550015718</v>
+        <v>0.2283506068786486</v>
       </c>
       <c r="C48">
-        <v>1.00623153048173</v>
+        <v>0.314141023151258</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.04027422376625769</v>
+        <v>-1.072995232615711</v>
       </c>
       <c r="C49">
-        <v>1.261603457658124</v>
+        <v>-0.6260083664142939</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.4951437272534046</v>
+        <v>-0.2761506304781433</v>
       </c>
       <c r="C50">
-        <v>-1.12563146471661</v>
+        <v>-0.1726786583276873</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.8846280737992867</v>
+        <v>0.1842238446965986</v>
       </c>
       <c r="C51">
-        <v>-2.125928841365064</v>
+        <v>0.1602573075118695</v>
       </c>
     </row>
   </sheetData>
